--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>264</v>
       </c>
       <c r="D2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D3">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>426</v>
